--- a/backtest_runs/20260410_193731/by_symbol/NRL/NRL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/NRL/NRL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-214.5600000000081</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>108016.2</v>
@@ -679,7 +679,7 @@
         <v>-4478.939999999991</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>103537.26</v>
@@ -909,7 +909,7 @@
         <v>-399.3200000000095</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>116291.66</v>
@@ -955,7 +955,7 @@
         <v>-5.959999999994579</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>116285.7</v>
@@ -1047,7 +1047,7 @@
         <v>-661.5600000000081</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>117483.66</v>
@@ -1093,7 +1093,7 @@
         <v>-1391.659999999988</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>116092</v>
@@ -1185,7 +1185,7 @@
         <v>-5119.640000000002</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>112015.36</v>
@@ -1231,7 +1231,7 @@
         <v>-3328.660000000005</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>108686.7</v>
@@ -1277,7 +1277,7 @@
         <v>-7035.780000000004</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>101650.92</v>
@@ -1507,7 +1507,7 @@
         <v>-1832.699999999993</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>119700.78</v>
@@ -1553,7 +1553,7 @@
         <v>-1594.300000000007</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>118106.48</v>
@@ -1645,7 +1645,7 @@
         <v>-2491.280000000004</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>124281.04</v>
